--- a/backend/tests/fixtures/listing_sample.xlsx
+++ b/backend/tests/fixtures/listing_sample.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +503,26 @@
           <t>Longitude</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Voter ID</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -569,6 +590,26 @@
       <c r="Q2" t="n">
         <v>77.6245</v>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Zoya Narang</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>395862397</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>MPSAnXINZQ</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -638,6 +679,26 @@
       <c r="Q3" t="n">
         <v>77.621</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Aarav Mehta</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>482913756</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>QLZbrTWMKD</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -707,6 +768,26 @@
       <c r="Q4" t="n">
         <v>77.6446</v>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Ishita Rao</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>917354628</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>XdRKmNPYUV</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -774,6 +855,26 @@
       <c r="Q5" t="n">
         <v>77.64</v>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Kabir Sethi</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>638201947</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>TnBWQZLKAF</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -840,6 +941,26 @@
       </c>
       <c r="Q6" t="n">
         <v>77.7499</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Meera Nair</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>504726183</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>HGpJVDXRCN</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
     </row>
   </sheetData>
